--- a/Mantenimiento/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/Mantenimiento/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -503,7 +498,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,7 +545,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -607,7 +592,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -659,7 +639,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -711,7 +686,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -763,7 +733,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -815,7 +780,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -867,7 +827,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -919,7 +874,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -971,7 +921,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1023,7 +968,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1075,7 +1015,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1127,7 +1062,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1179,7 +1109,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1231,7 +1156,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1283,7 +1203,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1335,7 +1250,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1387,7 +1297,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1439,7 +1344,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1491,7 +1391,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1543,7 +1438,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SAN_ROMAN</t>
+          <t>SAN ROMAN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1575,11 +1470,6 @@
       </c>
       <c r="K22" t="n">
         <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
+++ b/Mantenimiento/excels/PUNO-SAN_ROMAN-JULIACA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,61 +413,61 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>70536</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-15.487922</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-70.146288</v>
-      </c>
-      <c r="I2" t="n">
-        <v>840</v>
-      </c>
-      <c r="J2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-15.487922</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-70.146288</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>70545 TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-15.48968</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-70.127713</v>
-      </c>
-      <c r="I3" t="n">
-        <v>764</v>
-      </c>
-      <c r="J3" t="n">
-        <v>33</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-15.48968</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-70.127713</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>70546 SEÑOR DE HUANCA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-15.50498</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-70.12675</v>
-      </c>
-      <c r="I4" t="n">
-        <v>710</v>
-      </c>
-      <c r="J4" t="n">
-        <v>29</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-15.50498</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-70.12675</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>70547</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-15.484065</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-70.128818</v>
-      </c>
-      <c r="I5" t="n">
-        <v>865</v>
-      </c>
-      <c r="J5" t="n">
-        <v>38</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-15.484065</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-70.128818</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>70548</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-15.49226</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-70.14352</v>
-      </c>
-      <c r="I6" t="n">
-        <v>651</v>
-      </c>
-      <c r="J6" t="n">
-        <v>30</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-15.49226</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-70.14352</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>70564</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-15.48484</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-70.13979999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1002</v>
-      </c>
-      <c r="J7" t="n">
-        <v>41</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-15.48484</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-70.1398</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>70565 MARIANO NUÑEZ</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-15.49028</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-70.13373</v>
-      </c>
-      <c r="I8" t="n">
-        <v>914</v>
-      </c>
-      <c r="J8" t="n">
-        <v>37</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-15.49028</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-70.13373</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>70620</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-15.47849</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-70.13844</v>
-      </c>
-      <c r="I9" t="n">
-        <v>708</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-15.47849</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-70.13844</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>71014 MANUEL NUÑEZ BUTRON</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-15.499647</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-70.131946</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1384</v>
-      </c>
-      <c r="J10" t="n">
-        <v>62</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-15.499647</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-70.131946</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>71015 SAN JUAN BOSCO</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-15.49137</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-70.13106000000001</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1174</v>
-      </c>
-      <c r="J11" t="n">
-        <v>46</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-15.49137</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-70.13106</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -978,28 +1066,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>463892</t>
+          <t>463905</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>71016 MARIA AUXILIADORA</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>-15.49429</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-70.13477</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1522</v>
-      </c>
-      <c r="J12" t="n">
-        <v>58</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+          <t>LAS MERCEDES</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-15.490577</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-70.139012</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1025,28 +1123,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>463905</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LAS MERCEDES</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>-15.490577</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-70.13901199999999</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1990</v>
-      </c>
-      <c r="J13" t="n">
-        <v>84</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+          <t>JOSE ANTONIO ENCINAS</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-15.487692</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-70.124215</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1072,28 +1180,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>463948</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>JOSE ANTONIO ENCINAS</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>-15.487692</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70.12421500000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2807</v>
-      </c>
-      <c r="J14" t="n">
-        <v>131</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+          <t>32 MARIANO H. CORNEJO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-15.50433</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-70.12706</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1119,28 +1237,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>463934</t>
+          <t>463967</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>POLITECNICO REGIONAL LOS ANDES</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>-15.488678</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-70.143998</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2127</v>
-      </c>
-      <c r="J15" t="n">
-        <v>85</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+          <t>91 JOSE IGNACIO MIRANDA</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-15.512981</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-70.12539</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1166,28 +1294,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>463948</t>
+          <t>464108</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>32 MARIANO H. CORNEJO</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>-15.50433</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-70.12706</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1952</v>
-      </c>
-      <c r="J16" t="n">
-        <v>99</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+          <t>70708 COLIBRI / COLIBRI</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-15.49521</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-70.12807</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1213,28 +1351,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>463967</t>
+          <t>464189</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>91 JOSE IGNACIO MIRANDA</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>-15.512981</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-70.12539</v>
-      </c>
-      <c r="I17" t="n">
-        <v>670</v>
-      </c>
-      <c r="J17" t="n">
-        <v>37</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+          <t>SANTA CATALINA</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-15.49548</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-70.13702</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1260,28 +1408,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>464108</t>
+          <t>464226</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>70708 COLIBRI / COLIBRI</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>-15.49521</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-70.12806999999999</v>
-      </c>
-      <c r="I18" t="n">
-        <v>362</v>
-      </c>
-      <c r="J18" t="n">
-        <v>20</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+          <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-15.49249</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-70.1284</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1307,28 +1465,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>464189</t>
+          <t>464274</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SANTA CATALINA</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>-15.49548</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-70.13702000000001</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1176</v>
-      </c>
-      <c r="J19" t="n">
-        <v>44</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+          <t>PEDRO KALBERMATTER</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-15.49053</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-70.14365</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1354,122 +1522,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>464226</t>
+          <t>464293</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>LUZ ANDINA / LUZ ANDINA REYNA DE LAS AMERICAS</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>-15.49249</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-70.1284</v>
-      </c>
-      <c r="I20" t="n">
-        <v>547</v>
-      </c>
-      <c r="J20" t="n">
-        <v>44</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>464274</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>PEDRO KALBERMATTER</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>-15.49053</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-70.14364999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>342</v>
-      </c>
-      <c r="J21" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>211101</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>PUNO</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SAN ROMAN</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>JULIACA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>464293</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
           <t>TUPAC AMARU</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-15.49024</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-70.12615</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1291</v>
-      </c>
-      <c r="J22" t="n">
-        <v>61</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-15.49024</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-70.12615</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
